--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2949.2</v>
+        <v>2977.21</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8788.540000000001</v>
+        <v>8872.02</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3407.16</v>
+        <v>3439.53</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>23166.39</v>
+        <v>23386.45</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>63841.53</v>
+        <v>64447.96</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2564.9</v>
+        <v>2589.26</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1116.88</v>
+        <v>1127.49</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11365.79</v>
+        <v>11473.76</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2907.09</v>
+        <v>2934.7</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1721.55</v>
+        <v>1737.9</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4280.08</v>
+        <v>4320.74</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>40602.81</v>
+        <v>40761.31</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>57873.47</v>
+        <v>58099.38</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2528.66</v>
+        <v>2538.53</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2039.48</v>
+        <v>2047.44</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1341.77</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1373.53</v>
+        <v>1378.89</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3220.24</v>
+        <v>3232.81</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>861.3200000000001</v>
+        <v>864.6900000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>986.05</v>
+        <v>989.9</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2476.87</v>
+        <v>2486.54</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>813.48</v>
+        <v>816.66</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1777.52</v>
+        <v>1784.45</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1420</v>
+        <v>1425.54</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1572.23</v>
+        <v>1578.37</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4425.51</v>
+        <v>4442.79</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>62524.48</v>
+        <v>63153.32</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>37395.96</v>
+        <v>37772.07</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2407.28</v>
+        <v>2431.49</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>14503.82</v>
+        <v>14649.7</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3832.44</v>
+        <v>3870.98</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1698.39</v>
+        <v>1715.47</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6477.25</v>
+        <v>6542.39</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8805.43</v>
+        <v>8893.99</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5101.89</v>
+        <v>5153.2</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4033.96</v>
+        <v>4074.53</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>48169.35</v>
+        <v>48653.82</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4330.59</v>
+        <v>4374.15</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1483.2</v>
+        <v>1498.12</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>988.8</v>
+        <v>998.75</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2762.1</v>
+        <v>2789.88</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8610.370000000001</v>
+        <v>8696.969999999999</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>826.99</v>
+        <v>835.3</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1133.54</v>
+        <v>1144.94</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2823.62</v>
+        <v>2852.02</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4787.02</v>
+        <v>4835.17</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2431.35</v>
+        <v>2455.69</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>14472.31</v>
+        <v>14617.24</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1574.3</v>
+        <v>1590.06</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3360.74</v>
+        <v>3394.39</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6441.67</v>
+        <v>6506.18</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5364.12</v>
+        <v>5417.83</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>5446.41</v>
+        <v>5500.95</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>874.0599999999999</v>
+        <v>882.8099999999999</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>931.17</v>
+        <v>940.5</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>19789.47</v>
+        <v>19987.63</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1667.45</v>
+        <v>1684.14</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>977.04</v>
+        <v>986.8200000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>9767.940000000001</v>
+        <v>9865.75</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>827.22</v>
+        <v>835.51</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9072.92</v>
+        <v>9119.16</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1907.53</v>
+        <v>1917.25</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>778.14</v>
+        <v>782.1</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1661.75</v>
+        <v>1670.22</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4519.4</v>
+        <v>4542.43</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1591.4</v>
+        <v>1599.51</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7741</v>
+        <v>7780.45</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>952.83</v>
+        <v>957.6900000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1519.16</v>
+        <v>1526.9</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>72531.69</v>
+        <v>72901.3</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1588.43</v>
+        <v>1596.52</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1026.54</v>
+        <v>1031.77</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>893.49</v>
+        <v>898.04</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1876.25</v>
+        <v>1885.81</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>12760.88</v>
+        <v>12825.91</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>822.5</v>
+        <v>826.6900000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2749.79</v>
+        <v>2760.5</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1308.51</v>
+        <v>1313.6</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4109.28</v>
+        <v>4125.27</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2905.72</v>
+        <v>2917.03</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3811.52</v>
+        <v>3826.36</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>791.48</v>
+        <v>794.5700000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>10353.97</v>
+        <v>10394.28</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2258.84</v>
+        <v>2267.63</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7433.13</v>
+        <v>7462.06</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>915.73</v>
+        <v>919.29</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1308.51</v>
+        <v>1313.6</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5124.5</v>
+        <v>5144.45</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>15182.05</v>
+        <v>15241.15</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1991.04</v>
+        <v>1998.79</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1902.4</v>
+        <v>1909.81</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>6540.48</v>
+        <v>6565.94</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5103.57</v>
+        <v>5077.72</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>13087.61</v>
+        <v>13021.31</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2935.2</v>
+        <v>2920.33</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>14881.74</v>
+        <v>14806.36</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1681.14</v>
+        <v>1672.62</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>12484.4</v>
+        <v>12421.16</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>25651.62</v>
+        <v>25521.67</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8114.63</v>
+        <v>8073.52</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1333.46</v>
+        <v>1326.7</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3927.2</v>
+        <v>3907.3</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>7076.31</v>
+        <v>7040.47</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3827.25</v>
+        <v>3807.86</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5426.11</v>
+        <v>5398.63</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>12555.37</v>
+        <v>12491.77</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>17062.61</v>
+        <v>16976.17</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3518.77</v>
+        <v>3500.94</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5297.87</v>
+        <v>5309.16</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>16597.85</v>
+        <v>16633.22</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4990.2</v>
+        <v>5000.84</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1216.96</v>
+        <v>1219.55</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1124.7</v>
+        <v>1127.09</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>968.42</v>
+        <v>970.49</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>43395.69</v>
+        <v>43488.18</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1914.23</v>
+        <v>1918.31</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3228.35</v>
+        <v>3235.23</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3745.74</v>
+        <v>3753.73</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2135.3</v>
+        <v>2139.85</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1846.92</v>
+        <v>1850.86</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2530.91</v>
+        <v>2536.3</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>36229.24</v>
+        <v>36306.46</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>14509.42</v>
+        <v>14540.35</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4039.45</v>
+        <v>4048.06</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>820.65</v>
+        <v>822.39</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1251.83</v>
+        <v>1254.49</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3431.43</v>
+        <v>3438.75</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3433.14</v>
+        <v>3440.46</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3828.88</v>
+        <v>3853.84</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>819.38</v>
+        <v>824.72</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>775.3099999999999</v>
+        <v>780.36</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>8691.75</v>
+        <v>8748.42</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1747.48</v>
+        <v>1758.87</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1033.75</v>
+        <v>1040.49</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>837.36</v>
+        <v>842.8200000000001</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>6030.72</v>
+        <v>6070.04</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4014.94</v>
+        <v>4041.12</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>812</v>
+        <v>817.29</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>16099.1</v>
+        <v>16204.05</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>23201.61</v>
+        <v>23352.87</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>5001.7</v>
+        <v>5034.3</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>6847.7</v>
+        <v>6892.34</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3087.25</v>
+        <v>3107.37</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>11307.92</v>
+        <v>11381.64</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>791.4</v>
+        <v>796.5599999999999</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>12364.38</v>
+        <v>12444.99</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>811.3099999999999</v>
+        <v>816.6</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>19891.1</v>
+        <v>20020.78</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>9972.879999999999</v>
+        <v>10037.9</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1705.26</v>
+        <v>1716.37</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>807.84</v>
+        <v>809.6900000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>24775.29</v>
+        <v>24832.11</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>7906.98</v>
+        <v>7925.11</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>841.72</v>
+        <v>843.65</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2078.89</v>
+        <v>2083.65</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>4476.56</v>
+        <v>4486.82</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>815.0599999999999</v>
+        <v>816.9299999999999</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4643.43</v>
+        <v>4654.08</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1093.8</v>
+        <v>1096.31</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3367.72</v>
+        <v>3375.45</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>6263.36</v>
+        <v>6277.72</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3807.24</v>
+        <v>3815.97</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>792.62</v>
+        <v>794.4400000000001</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1310.14</v>
+        <v>1313.14</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1695.33</v>
+        <v>1699.21</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>838.4299999999999</v>
+        <v>840.35</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4109.28</v>
+        <v>4118.7</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3450.35</v>
+        <v>3473.44</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2236.98</v>
+        <v>2251.95</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2617.19</v>
+        <v>2634.71</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>7636.23</v>
+        <v>7687.34</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>14721.07</v>
+        <v>14819.6</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1077.37</v>
+        <v>1084.58</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>8690.41</v>
+        <v>8748.57</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1912.45</v>
+        <v>1925.25</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>33489.74</v>
+        <v>33713.91</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>7955.23</v>
+        <v>8008.48</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5033.95</v>
+        <v>5067.65</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3296.72</v>
+        <v>3318.79</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>982.8</v>
+        <v>989.38</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>22462.77</v>
+        <v>22613.13</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>16009.72</v>
+        <v>16116.88</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2614.63</v>
+        <v>2632.13</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>17658.84</v>
+        <v>17777.04</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2189.94</v>
+        <v>2204.59</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>7116.7</v>
+        <v>7164.33</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1718.4</v>
+        <v>1729.9</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1669.62</v>
+        <v>1680.8</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>9614.379999999999</v>
+        <v>9678.74</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3066.06</v>
+        <v>3086.58</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5258.19</v>
+        <v>5293.38</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1395.83</v>
+        <v>1405.18</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2081.79</v>
+        <v>2095.72</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>4314.82</v>
+        <v>4343.7</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1481.06</v>
+        <v>1490.97</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>3445.61</v>
+        <v>3468.68</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2934.7</v>
+        <v>2954.35</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>16122.18</v>
+        <v>16230.09</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2753.05</v>
+        <v>2771.47</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>778.67</v>
+        <v>783.88</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>8412.92</v>
+        <v>8469.23</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1037.54</v>
+        <v>1044.49</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2284.87</v>
+        <v>2300.16</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2086.18</v>
+        <v>2100.78</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>901.16</v>
+        <v>907.46</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2503.55</v>
+        <v>2521.08</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>3235.95</v>
+        <v>3258.6</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>982.3200000000001</v>
+        <v>989.2</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>5715.18</v>
+        <v>5755.17</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1236</v>
+        <v>1244.65</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>9117.1</v>
+        <v>9180.91</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3593.32</v>
+        <v>3618.46</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>819.22</v>
+        <v>824.96</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>18405.07</v>
+        <v>18533.88</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1759.93</v>
+        <v>1772.24</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1002.3</v>
+        <v>1009.31</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>37880.29</v>
+        <v>38145.39</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>798.78</v>
+        <v>804.37</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>33080.65</v>
+        <v>33312.16</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1060.43</v>
+        <v>1067.85</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>18584.69</v>
+        <v>18714.75</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2902.83</v>
+        <v>2923.14</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>986.05</v>
+        <v>992.95</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>18239.29</v>
+        <v>18366.93</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>7726.94</v>
+        <v>7781.02</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>856.3099999999999</v>
+        <v>862.3</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>781</v>
+        <v>778.54</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>5999.72</v>
+        <v>5980.77</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>776.9299999999999</v>
+        <v>774.47</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>21096.02</v>
+        <v>21029.38</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>4633.92</v>
+        <v>4619.28</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1125.97</v>
+        <v>1122.41</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>920.42</v>
+        <v>917.51</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>21430.51</v>
+        <v>21362.82</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>11351.23</v>
+        <v>11315.37</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>6111.57</v>
+        <v>6092.26</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>776.9299999999999</v>
+        <v>774.47</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>27243.89</v>
+        <v>27157.83</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1167</v>
+        <v>1163.32</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1376.81</v>
+        <v>1372.47</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2355.15</v>
+        <v>2347.71</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>11120.66</v>
+        <v>11085.53</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>780.54</v>
+        <v>778.08</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2117.9</v>
+        <v>2111.21</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1018.75</v>
+        <v>1016.54</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1615.19</v>
+        <v>1611.68</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>773.6900000000001</v>
+        <v>772.01</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2162.48</v>
+        <v>2157.77</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>5973.14</v>
+        <v>5960.14</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1739.77</v>
+        <v>1735.98</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3031.09</v>
+        <v>3024.49</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2174.6</v>
+        <v>2169.87</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1470.67</v>
+        <v>1467.47</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1739.77</v>
+        <v>1735.98</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>6436.74</v>
+        <v>6422.74</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>986.9299999999999</v>
+        <v>984.78</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2453.06</v>
+        <v>2447.73</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>29789.87</v>
+        <v>29725.06</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>7123.88</v>
+        <v>7108.38</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>28549.8</v>
+        <v>28487.68</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1142.29</v>
+        <v>1139.81</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>824.5700000000001</v>
+        <v>822.78</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1513.43</v>
+        <v>1510.14</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>3604.13</v>
+        <v>3596.29</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1197.59</v>
+        <v>1195.19</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>4018.92</v>
+        <v>4010.86</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>6863.12</v>
+        <v>6849.36</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1884.73</v>
+        <v>1880.96</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>10141.07</v>
+        <v>10120.74</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1181.09</v>
+        <v>1178.72</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3620.13</v>
+        <v>3612.87</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2259.96</v>
+        <v>2255.43</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>8672.959999999999</v>
+        <v>8655.58</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1536.43</v>
+        <v>1533.35</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>941.0599999999999</v>
+        <v>939.17</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>936.6</v>
+        <v>934.73</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1768.56</v>
+        <v>1765.01</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2913.84</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5763.19</v>
+        <v>5751.63</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>46984.66</v>
+        <v>46890.47</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>5176.86</v>
+        <v>5166.48</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1302.19</v>
+        <v>1299.58</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2363.1</v>
+        <v>2358.36</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>825.3200000000001</v>
+        <v>823.67</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1643.71</v>
+        <v>1634.2</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>3722.35</v>
+        <v>3700.81</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>965.8099999999999</v>
+        <v>960.22</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>5295.89</v>
+        <v>5265.24</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>997.02</v>
+        <v>991.25</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>8451.139999999999</v>
+        <v>8402.219999999999</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>16294.19</v>
+        <v>16199.88</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2324.34</v>
+        <v>2310.89</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>964.9299999999999</v>
+        <v>959.34</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>863.74</v>
+        <v>858.74</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>37829.8</v>
+        <v>37610.83</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1731.91</v>
+        <v>1721.89</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2573.03</v>
+        <v>2558.13</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>962.38</v>
+        <v>946.85</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1571.66</v>
+        <v>1546.29</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1468.62</v>
+        <v>1444.92</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1867.63</v>
+        <v>1837.49</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>11647.51</v>
+        <v>11459.55</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>4590.53</v>
+        <v>4516.45</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>6883.69</v>
+        <v>6772.6</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1448.06</v>
+        <v>1424.69</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>5003.27</v>
+        <v>4922.53</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>7694.78</v>
+        <v>7570.6</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2524.08</v>
+        <v>2483.34</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>6405.87</v>
+        <v>6302.5</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2179.06</v>
+        <v>2143.89</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>857.27</v>
+        <v>843.53</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>3727.34</v>
+        <v>3667.58</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>1071.3</v>
+        <v>1054.13</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1150.41</v>
+        <v>1131.97</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1142.88</v>
+        <v>1124.55</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>802.4299999999999</v>
+        <v>789.5599999999999</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>11003.3</v>
+        <v>10826.88</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>12568.32</v>
+        <v>12366.81</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>4978.73</v>
+        <v>4898.91</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>774.04</v>
+        <v>761.63</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>6616.9</v>
+        <v>6510.81</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8455.41</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>9406.9</v>
+        <v>9256.07</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2393.83</v>
+        <v>2355.45</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>26013.68</v>
+        <v>25596.59</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>2497.16</v>
+        <v>2457.12</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>4504.55</v>
+        <v>4432.33</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>8428.440000000001</v>
+        <v>8293.299999999999</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>16647.77</v>
+        <v>16380.85</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1220.72</v>
+        <v>1206.51</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>66313.69</v>
+        <v>65542.09</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>4575.16</v>
+        <v>4521.92</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>782.61</v>
+        <v>773.5</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1921.53</v>
+        <v>1899.18</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1748.63</v>
+        <v>1728.28</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2228.86</v>
+        <v>2202.93</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>3905.01</v>
+        <v>3859.58</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>961.72</v>
+        <v>950.53</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>3338.12</v>
+        <v>3299.27</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>7265.02</v>
+        <v>7180.49</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>3895.9</v>
+        <v>3850.57</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>5139.43</v>
+        <v>5079.63</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2562.35</v>
+        <v>2532.54</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1130.79</v>
+        <v>1117.63</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>26758.66</v>
+        <v>26447.3</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2458.05</v>
+        <v>2429.45</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>781</v>
+        <v>776.67</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>27208.18</v>
+        <v>27057.34</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2292.62</v>
+        <v>2279.91</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>6527.1</v>
+        <v>6490.92</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1234.72</v>
+        <v>1227.87</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>4937.19</v>
+        <v>4909.82</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>8946.379999999999</v>
+        <v>8896.780000000001</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>5824.3</v>
+        <v>5792.02</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3745.23</v>
+        <v>3724.47</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>23130.85</v>
+        <v>23002.61</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1315.31</v>
+        <v>1308.01</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1310.69</v>
+        <v>1303.42</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>3326.38</v>
+        <v>3307.94</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>3067.53</v>
+        <v>3050.52</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2745.95</v>
+        <v>2732.45</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>38109.25</v>
+        <v>37921.88</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>1816.4</v>
+        <v>1807.47</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1752.57</v>
+        <v>1743.95</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>4368.05</v>
+        <v>4346.57</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1158.87</v>
+        <v>1153.18</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2486.17</v>
+        <v>2473.95</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>885.8200000000001</v>
+        <v>881.46</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1186.23</v>
+        <v>1180.4</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>31864.91</v>
+        <v>31708.23</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1562.27</v>
+        <v>1554.58</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>35342</v>
+        <v>35168.23</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>995.6</v>
+        <v>990.71</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>7458.51</v>
+        <v>7421.84</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>3614.21</v>
+        <v>3638.41</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>30982.82</v>
+        <v>31190.2</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1838.3</v>
+        <v>1850.6</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>12565.83</v>
+        <v>12649.94</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>7660.98</v>
+        <v>7712.26</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>40220.51</v>
+        <v>40489.72</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>42964.07</v>
+        <v>43251.65</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>4259.04</v>
+        <v>4287.55</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1363.75</v>
+        <v>1372.88</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1877.05</v>
+        <v>1889.62</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>4325.68</v>
+        <v>4354.63</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2353.87</v>
+        <v>2369.62</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>3395.64</v>
+        <v>3418.36</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>1580.86</v>
+        <v>1591.44</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>51671.44</v>
+        <v>52017.3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1119,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1184,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1310,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1558,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1623,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2054,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2119,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2489,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2554,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2619,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2684,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2871,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2936,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3001,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3066,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3375,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3440,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3688,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4119,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4184,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4249,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4558,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4623,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4749,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4814,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5123,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5493,11 @@
           <t>77.724.409-4</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5680,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5745,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6115,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6180,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6245,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6310,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6497,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6562,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6627,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6875,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6940,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7005,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7131,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7379,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7444,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7570,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7635,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7700,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8009,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8135,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8200,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8387,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8452,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8578,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8887,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9013,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9078,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9143,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9269,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9395,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9643,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9708,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9773,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9899,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9964,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10090,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10155,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10220,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10285,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10472,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10842,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10968,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11155,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11281,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11468,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11533,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11598,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11724,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11911,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11976,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12102,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12167,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12232,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12297,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12545,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12671,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12858,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12923,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13049,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13236,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13484,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13610,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13675,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13740,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13805,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13931,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +13996,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14061,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14309,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14435,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14500,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14626,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14691,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15305,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15370,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15496,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15744,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16602,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16667,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16793,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16858,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17045,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17110,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17785,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +17850,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18098,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18407,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18533,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18598,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18663,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +18850,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +18915,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +18980,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19106,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19171,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19358,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19423,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19793,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +19919,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +19984,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20171,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20358,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20545,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20610,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +20858,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21228,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21476,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21541,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21606,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21732,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +21919,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22045,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22354,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22480,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22667,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +22732,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +22797,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +22862,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23110,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23480,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23545,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23671,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +23736,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24106,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24171,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +24663,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +24789,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +24915,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25163,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25289,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
@@ -3814,7 +3814,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11346,7 +11350,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23297,7 +23305,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M398"/>
+  <dimension ref="A1:M400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3085-451-CM26</t>
+          <t>2343-330-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11648,27 +11648,27 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.102.023-6</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3318.79</v>
+        <v>5067.65</v>
       </c>
     </row>
     <row r="180">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -12001,7 +12001,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2343-330-CM26</t>
+          <t>3085-451-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12026,27 +12026,27 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.102.023-6</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.750.890-3</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5067.65</v>
+        <v>3318.79</v>
       </c>
     </row>
     <row r="186">
@@ -12257,7 +12257,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>4077-106-CM26</t>
+          <t>1078078-1901-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12282,47 +12282,43 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>9678.74</v>
+        <v>4343.7</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1078078-1901-CM26</t>
+          <t>4077-106-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12342,42 +12338,46 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>4343.7</v>
+        <v>9678.74</v>
       </c>
     </row>
     <row r="191">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -14716,7 +14716,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1078078-2104-CM26</t>
+          <t>3710-442-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14736,48 +14736,52 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>5980.77</v>
+        <v>21362.82</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2358-261-CM26</t>
+          <t>1078078-2104-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14802,27 +14806,27 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14832,7 +14836,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>778.54</v>
+        <v>5980.77</v>
       </c>
     </row>
     <row r="230">
@@ -14919,7 +14923,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -15163,7 +15167,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -15224,7 +15228,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -15265,7 +15269,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3710-442-CM26</t>
+          <t>2358-261-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15290,41 +15294,37 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.750.890-3</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>21362.82</v>
+        <v>778.54</v>
       </c>
     </row>
     <row r="238">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -16155,7 +16155,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -16257,7 +16257,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1078078-2137-CM26</t>
+          <t>2432-482-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16277,17 +16277,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16297,12 +16297,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -16312,7 +16312,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1735.98</v>
+        <v>772.01</v>
       </c>
     </row>
     <row r="254">
@@ -16501,7 +16501,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2432-482-CM26</t>
+          <t>1078078-2137-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16526,12 +16526,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16541,12 +16541,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16556,7 +16556,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>772.01</v>
+        <v>1735.98</v>
       </c>
     </row>
     <row r="258">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -17196,7 +17196,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5349-1418-CM26</t>
+          <t>4494-516-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17216,32 +17216,32 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>77.750.890-3</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1195.19</v>
+        <v>2255.43</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2561-251-CM26</t>
+          <t>5349-1418-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17282,27 +17282,27 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.004.035-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -17312,13 +17312,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>4010.86</v>
+        <v>1195.19</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2561-252-CM26</t>
+          <t>2561-251-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17358,12 +17358,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -17373,13 +17373,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>6849.36</v>
+        <v>4010.86</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1078078-2155-CM26</t>
+          <t>2561-252-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17399,17 +17399,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.004.035-7</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17419,12 +17419,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -17434,13 +17434,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1880.96</v>
+        <v>6849.36</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>707422-111-CM26</t>
+          <t>1078078-2155-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17465,27 +17465,27 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -17495,13 +17495,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>10120.74</v>
+        <v>1880.96</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>48-176-CM26</t>
+          <t>707422-111-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17526,27 +17526,27 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17556,13 +17556,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1178.72</v>
+        <v>10120.74</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1461054-282-CM26</t>
+          <t>48-176-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17582,32 +17582,32 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17617,13 +17617,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3612.87</v>
+        <v>1178.72</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>4494-516-CM26</t>
+          <t>1461054-282-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17648,27 +17648,27 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2255.43</v>
+        <v>3612.87</v>
       </c>
     </row>
     <row r="276">
@@ -17810,7 +17810,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2287-572-CM26</t>
+          <t>5770-17-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17830,17 +17830,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.253.700-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17850,32 +17850,28 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>J RAVERA Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.780.200-3</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>939.17</v>
+        <v>934.73</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5770-17-CM26</t>
+          <t>2287-572-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17895,17 +17891,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.253.700-9</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17915,22 +17911,26 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>J RAVERA Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>80.780.200-3</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>934.73</v>
+        <v>939.17</v>
       </c>
     </row>
     <row r="280">
@@ -17956,7 +17956,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -18452,7 +18452,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -18810,7 +18810,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2345-327-CM26</t>
+          <t>1432083-1689-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18835,47 +18835,43 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>959.34</v>
+        <v>2558.13</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1432083-1682-CM26</t>
+          <t>4085-471-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18895,37 +18891,37 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -18934,13 +18930,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2310.89</v>
+        <v>6694.05</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2345-326-CM26</t>
+          <t>2345-327-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18980,12 +18976,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -18999,13 +18995,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>858.74</v>
+        <v>959.34</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2345-324-CM26</t>
+          <t>2345-326-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19045,28 +19041,32 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr"/>
+          <t>77.610.398-5</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>16199.88</v>
+        <v>858.74</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2345-317-CM26</t>
+          <t>2345-324-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -19106,32 +19106,28 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>37610.83</v>
+        <v>16199.88</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1951-501-CM26</t>
+          <t>2345-317-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19151,37 +19147,37 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.602.246-6</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR HOSPITAL CARAHUE</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -19190,13 +19186,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1721.89</v>
+        <v>37610.83</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1432083-1689-CM26</t>
+          <t>1951-501-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19216,48 +19212,52 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.602.246-6</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR HOSPITAL CARAHUE</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2558.13</v>
+        <v>1721.89</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5434-231-CM26</t>
+          <t>1432083-1682-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -19282,43 +19282,47 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>946.85</v>
+        <v>2310.89</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2173-191-CM26</t>
+          <t>5434-231-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19338,17 +19342,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19358,32 +19362,28 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1546.29</v>
+        <v>946.85</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4734-118-CM26</t>
+          <t>2173-191-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19408,32 +19408,32 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -19442,13 +19442,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1444.92</v>
+        <v>1546.29</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1057541-638-CM26</t>
+          <t>4734-118-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19473,43 +19473,47 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.265.000-k</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1837.49</v>
+        <v>1444.92</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1113403-132-CM26</t>
+          <t>1057541-638-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19529,32 +19533,32 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>62.000.650-5</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE GABRIELA MISTRAL</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -19564,13 +19568,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>11459.55</v>
+        <v>1837.49</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1078078-2238-CM26</t>
+          <t>1113403-132-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19590,17 +19594,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>62.000.650-5</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE GABRIELA MISTRAL</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19610,12 +19614,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -19625,7 +19629,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>4516.45</v>
+        <v>11459.55</v>
       </c>
     </row>
     <row r="307">
@@ -19692,7 +19696,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2674-631-CM26</t>
+          <t>1233600-386-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19717,12 +19721,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>70.931.100-K</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>CORP MUNICIPAL DE RENCA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19732,12 +19736,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19747,13 +19751,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2143.89</v>
+        <v>823.13</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1446646-23-CM26</t>
+          <t>1078078-2238-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19778,47 +19782,43 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>69.180.500-K</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1424.69</v>
+        <v>4516.45</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5153-1284-CM26</t>
+          <t>1446646-23-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19838,48 +19838,52 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.180.500-K</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>4922.53</v>
+        <v>1424.69</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5061-413-CM26</t>
+          <t>5153-1284-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19904,47 +19908,43 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>7570.6</v>
+        <v>4922.53</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>960841-43-CM26</t>
+          <t>5061-413-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19969,12 +19969,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>69.180.500-K</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19984,17 +19984,17 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -20003,13 +20003,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2483.34</v>
+        <v>7570.6</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>3316-79-CM26</t>
+          <t>760-234-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20034,43 +20034,47 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
-        </is>
-      </c>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>6302.5</v>
+        <v>2392.06</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1233600-386-CM26</t>
+          <t>960841-43-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20090,48 +20094,52 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>70.931.100-K</t>
+          <t>69.180.500-K</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE RENCA</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>823.13</v>
+        <v>2483.34</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>3191-3810-CM26</t>
+          <t>3316-79-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20146,57 +20154,53 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>843.53</v>
+        <v>6302.5</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3922-653-CM26</t>
+          <t>2674-631-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20211,37 +20215,37 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -20251,13 +20255,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>3667.58</v>
+        <v>2143.89</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>539119-2449-CM26</t>
+          <t>3191-3810-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20277,48 +20281,52 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K317" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1054.13</v>
+        <v>843.53</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5194-208-CM26</t>
+          <t>3922-653-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20343,47 +20351,43 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>61.004.108-6</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>96.355.000-6</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1131.97</v>
+        <v>3667.58</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>539119-2445-CM26</t>
+          <t>539119-2449-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20403,7 +20407,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -20438,13 +20442,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1124.55</v>
+        <v>1054.13</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1360-108-CM26</t>
+          <t>5194-208-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20464,17 +20468,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.960.900-K</t>
+          <t>61.004.108-6</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20484,28 +20488,32 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>789.5599999999999</v>
+        <v>1131.97</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>4404-165-CM26</t>
+          <t>539119-2445-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20530,47 +20538,43 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>10826.88</v>
+        <v>1124.55</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5807-141-CM26</t>
+          <t>1360-108-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20590,17 +20594,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.960.900-K</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20610,32 +20614,28 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>INVERSIONES CHILE LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>77.795.374-5</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>12366.81</v>
+        <v>789.5599999999999</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1078078-2294-CM26</t>
+          <t>4404-165-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20655,48 +20655,52 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>4898.91</v>
+        <v>10826.88</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1422051-249-CM26</t>
+          <t>5807-141-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20721,12 +20725,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20736,28 +20740,32 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>INVERSIONES CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr"/>
+          <t>77.795.374-5</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>761.63</v>
+        <v>12366.81</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1422051-252-CM26</t>
+          <t>1078078-2294-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20782,12 +20790,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20797,12 +20805,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -20812,13 +20820,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>6510.81</v>
+        <v>4898.91</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>3385-178-CM26</t>
+          <t>1422051-248-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20843,47 +20851,43 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>8455.41</v>
+        <v>2355.45</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1422051-247-CM26</t>
+          <t>1422051-252-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20923,12 +20927,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>J RAVERA Y COMPANIA LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>80.780.200-3</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K327" t="inlineStr"/>
@@ -20938,13 +20942,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>9256.07</v>
+        <v>6510.81</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1422051-248-CM26</t>
+          <t>3385-178-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20969,43 +20973,47 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2355.45</v>
+        <v>8455.41</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2974-223-CM26</t>
+          <t>1422051-247-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21025,17 +21033,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21045,12 +21053,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>J RAVERA Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>80.780.200-3</t>
         </is>
       </c>
       <c r="K329" t="inlineStr"/>
@@ -21060,13 +21068,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>25596.59</v>
+        <v>9256.07</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>757-401-CM26</t>
+          <t>1422051-249-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21091,12 +21099,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21121,13 +21129,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2457.12</v>
+        <v>761.63</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1572-78-CM26</t>
+          <t>2974-223-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21152,27 +21160,27 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K331" t="inlineStr"/>
@@ -21182,13 +21190,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>4432.33</v>
+        <v>25596.59</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>568658-1133-CM26</t>
+          <t>757-401-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21213,47 +21221,43 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>8293.299999999999</v>
+        <v>2457.12</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>5195-133-CM26</t>
+          <t>1572-78-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21278,17 +21282,17 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>65.743.680-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -21308,13 +21312,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>16380.85</v>
+        <v>4432.33</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1422051-255-CM26</t>
+          <t>568658-1133-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21329,53 +21333,57 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>J RAVERA Y COMPANIA LIMITADA</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>80.780.200-3</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1206.51</v>
+        <v>8293.299999999999</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1375761-1335-CM26</t>
+          <t>5195-133-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21390,7 +21398,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -21400,27 +21408,27 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>65.743.680-1</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K335" t="inlineStr"/>
@@ -21430,13 +21438,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>65542.09</v>
+        <v>16380.85</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>3756-523-CM26</t>
+          <t>1422051-255-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -21456,52 +21464,48 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>J RAVERA Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>80.780.200-3</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>4521.92</v>
+        <v>1206.51</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1774-91-CM26</t>
+          <t>1375761-1335-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21521,52 +21525,48 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.290.943-K</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>773.5</v>
+        <v>65542.09</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2446-852-CM26</t>
+          <t>3756-523-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21586,22 +21586,22 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21625,13 +21625,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>2202.93</v>
+        <v>4521.92</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1062018-164-CM26</t>
+          <t>1774-91-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21651,48 +21651,52 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>62.000.410-3</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DEFENSORIA DE LOS DERECHOS DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>76.691.662-7</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1728.28</v>
+        <v>773.5</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1422051-256-CM26</t>
+          <t>2446-852-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21712,37 +21716,37 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -21751,13 +21755,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>950.53</v>
+        <v>2202.93</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1562-273-CM26</t>
+          <t>1062018-164-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21777,17 +21781,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>62.000.410-3</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>DEFENSORIA DE LOS DERECHOS DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21812,13 +21816,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3859.58</v>
+        <v>1728.28</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1018-105-CM26</t>
+          <t>1422051-256-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21843,12 +21847,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21858,28 +21862,32 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1899.18</v>
+        <v>950.53</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2852-719-CM26</t>
+          <t>1562-273-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21899,52 +21907,48 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>3299.27</v>
+        <v>3859.58</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>4236-506-CM26</t>
+          <t>1018-105-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21964,32 +21968,32 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -21999,13 +22003,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>7180.49</v>
+        <v>1899.18</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1232366-87-CM26</t>
+          <t>2852-719-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22025,52 +22029,52 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>3850.57</v>
+        <v>3299.27</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1702-462-CM26</t>
+          <t>4236-506-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22090,32 +22094,32 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>61.606.605-6</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K346" t="inlineStr"/>
@@ -22125,13 +22129,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>5079.63</v>
+        <v>7180.49</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1430715-156-CM26</t>
+          <t>1232366-87-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22151,48 +22155,52 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2532.54</v>
+        <v>3850.57</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>4051-140-CM26</t>
+          <t>1702-462-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22212,32 +22220,32 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.606.605-6</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -22247,13 +22255,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1117.63</v>
+        <v>5079.63</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2408-602-CM26</t>
+          <t>1430715-156-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22278,27 +22286,27 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -22308,13 +22316,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>26447.3</v>
+        <v>2532.54</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>3512-694-CM26</t>
+          <t>4051-140-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22339,47 +22347,43 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2429.45</v>
+        <v>1117.63</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2358-282-CM26</t>
+          <t>2408-602-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22394,22 +22398,22 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -22419,12 +22423,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K351" t="inlineStr"/>
@@ -22434,13 +22438,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>776.67</v>
+        <v>26447.3</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>4455-485-CM26</t>
+          <t>3512-694-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -22455,7 +22459,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -22465,32 +22469,32 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -22499,13 +22503,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>27057.34</v>
+        <v>2429.45</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1432083-1810-CM26</t>
+          <t>2358-282-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22525,32 +22529,32 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.750.890-3</t>
         </is>
       </c>
       <c r="K353" t="inlineStr"/>
@@ -22560,13 +22564,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2279.91</v>
+        <v>776.67</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>3085-483-CM26</t>
+          <t>4455-485-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22591,12 +22595,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>61.102.023-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22606,28 +22610,32 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr"/>
+          <t>77.819.582-8</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>6490.92</v>
+        <v>27057.34</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2341-358-CM26</t>
+          <t>1432083-1810-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22647,52 +22655,48 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1227.87</v>
+        <v>2279.91</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1078078-2387-CM26</t>
+          <t>3085-483-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22712,52 +22716,48 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.102.023-6</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.750.890-3</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>4909.82</v>
+        <v>6490.92</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2389-412-CM26</t>
+          <t>2341-358-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22782,32 +22782,32 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -22816,13 +22816,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>8896.780000000001</v>
+        <v>1227.87</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1802-76-CM26</t>
+          <t>1078078-2387-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22847,47 +22847,47 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
           <t>Araucanía</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
-        </is>
-      </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>5383.7</v>
+        <v>4909.82</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>5178-3285-CM26</t>
+          <t>2389-412-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22907,48 +22907,52 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>J RAVERA Y COMPANIA LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>80.780.200-3</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>5792.02</v>
+        <v>8896.780000000001</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2672-15-CM26</t>
+          <t>1802-76-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22973,43 +22977,47 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>3724.47</v>
+        <v>5383.7</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1027-59-CM26</t>
+          <t>5178-3285-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23029,32 +23037,32 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>J RAVERA Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>80.780.200-3</t>
         </is>
       </c>
       <c r="K361" t="inlineStr"/>
@@ -23064,13 +23072,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>23002.61</v>
+        <v>5792.02</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2799-733-CM26</t>
+          <t>2672-15-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23095,47 +23103,43 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1308.01</v>
+        <v>3724.47</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>5195-134-CM26</t>
+          <t>1027-59-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23155,32 +23159,32 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>65.743.680-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -23190,13 +23194,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1303.42</v>
+        <v>23002.61</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>3712-519-CM26</t>
+          <t>2799-733-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23216,48 +23220,52 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr"/>
+          <t>76.532.399-1</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>9873.530000000001</v>
+        <v>1308.01</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2173-186-CM26</t>
+          <t>5195-134-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23277,17 +23285,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>65.743.680-1</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -23297,32 +23305,28 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>3307.94</v>
+        <v>1303.42</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1216088-183-CM26</t>
+          <t>3712-519-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23347,27 +23351,27 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>76.206.192-9</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K366" t="inlineStr"/>
@@ -23377,13 +23381,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>3050.52</v>
+        <v>9873.530000000001</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2755-320-CM26</t>
+          <t>2173-186-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23398,7 +23402,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -23408,43 +23412,47 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>11.647.874-9</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1743.95</v>
+        <v>3307.94</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>5548-124-CM26</t>
+          <t>1216088-183-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -23459,7 +23467,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -23469,12 +23477,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>65.065.121-9</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -23484,32 +23492,28 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.206.192-9</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2732.45</v>
+        <v>3050.52</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2852-735-CM26</t>
+          <t>2755-320-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -23529,52 +23533,48 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>11.647.874-9</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>37921.88</v>
+        <v>1743.95</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>3509-302-CM26</t>
+          <t>5548-124-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -23594,48 +23594,52 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>4430.78</v>
+        <v>2732.45</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2920-161-CM26</t>
+          <t>2852-735-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -23655,37 +23659,37 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -23694,13 +23698,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1807.47</v>
+        <v>37921.88</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2427-660-CM26</t>
+          <t>3509-302-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23725,47 +23729,43 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>4346.57</v>
+        <v>4430.78</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2513-29-CM26</t>
+          <t>2920-161-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -23785,17 +23785,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.252.300-8</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23805,28 +23805,32 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K373" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>1153.18</v>
+        <v>1807.47</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1211839-477-CM26</t>
+          <t>2427-660-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23851,43 +23855,47 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr">
-        <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="J374" t="inlineStr">
-        <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>881.46</v>
+        <v>4346.57</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>633-414-CM26</t>
+          <t>2513-29-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23907,7 +23915,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -23922,7 +23930,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23942,13 +23950,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>7421.84</v>
+        <v>1153.18</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2448-779-CM26</t>
+          <t>1211839-477-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -23968,32 +23976,32 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K376" t="inlineStr"/>
@@ -24003,13 +24011,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1180.4</v>
+        <v>881.46</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1134432-543-CM26</t>
+          <t>633-414-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24034,27 +24042,27 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>11.647.874-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K377" t="inlineStr"/>
@@ -24064,13 +24072,13 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>31708.23</v>
+        <v>7421.84</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1426099-149-CM26</t>
+          <t>2448-779-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24095,47 +24103,43 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1554.58</v>
+        <v>1180.4</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1195-403-CM26</t>
+          <t>1134432-543-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24160,47 +24164,43 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K379" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.647.874-9</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>35168.23</v>
+        <v>31708.23</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2273-438-CM26</t>
+          <t>1426099-149-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -24220,48 +24220,52 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
-        </is>
-      </c>
-      <c r="J380" t="inlineStr">
-        <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>990.71</v>
+        <v>1554.58</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>633-415-CM26</t>
+          <t>1195-403-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24281,48 +24285,52 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
-        </is>
-      </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2473.95</v>
+        <v>35168.23</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1658-2176-CM26</t>
+          <t>2273-438-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -24337,37 +24345,37 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguridad Industrial SPA </t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>76.756.768-5</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K382" t="inlineStr"/>
@@ -24377,13 +24385,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>3638.41</v>
+        <v>990.71</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1028-234-CM26</t>
+          <t>633-415-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -24398,37 +24406,37 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K383" t="inlineStr"/>
@@ -24438,13 +24446,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>31190.2</v>
+        <v>2473.95</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>3275-7161-CM26</t>
+          <t>1658-2176-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -24469,27 +24477,27 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.756.768-5</t>
         </is>
       </c>
       <c r="K384" t="inlineStr"/>
@@ -24499,13 +24507,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1850.6</v>
+        <v>3638.41</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1028-233-CM26</t>
+          <t>1028-234-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -24545,12 +24553,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>99.590.760-7</t>
         </is>
       </c>
       <c r="K385" t="inlineStr"/>
@@ -24560,13 +24568,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>12649.94</v>
+        <v>31190.2</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2408-696-CM26</t>
+          <t>3275-7161-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -24591,27 +24599,27 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K386" t="inlineStr"/>
@@ -24621,13 +24629,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>7712.26</v>
+        <v>1850.6</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2958-50-CM26</t>
+          <t>1028-233-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24652,12 +24660,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.102.011-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24667,32 +24675,28 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.397.758-7</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>40489.72</v>
+        <v>12649.94</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1432083-1838-CM26</t>
+          <t>2408-696-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -24712,32 +24716,32 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K388" t="inlineStr"/>
@@ -24747,13 +24751,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1591.44</v>
+        <v>7712.26</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1233616-1387-CM26</t>
+          <t>2958-50-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -24773,37 +24777,37 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.102.011-2</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -24812,13 +24816,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>43251.65</v>
+        <v>40489.72</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2429-907-CM26</t>
+          <t>1432083-1838-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -24843,27 +24847,27 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K390" t="inlineStr"/>
@@ -24873,13 +24877,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>38414.77</v>
+        <v>1591.44</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2378-264-CM26</t>
+          <t>1233616-1387-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -24899,37 +24903,37 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -24938,13 +24942,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>4287.55</v>
+        <v>43251.65</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1426038-194-CM26</t>
+          <t>2429-907-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -24969,27 +24973,27 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Colina</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K392" t="inlineStr"/>
@@ -24999,13 +25003,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1372.88</v>
+        <v>38414.77</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>3275-7159-CM26</t>
+          <t>2378-264-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25030,43 +25034,47 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K393" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>1889.62</v>
+        <v>4287.55</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1063796-29-CM26</t>
+          <t>1426038-194-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25091,27 +25099,27 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>69.150.400-k</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K394" t="inlineStr"/>
@@ -25121,13 +25129,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>4354.63</v>
+        <v>1372.88</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2345-323-CM26</t>
+          <t>3275-7159-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25147,52 +25155,48 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K395" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2369.62</v>
+        <v>1889.62</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1078078-2477-CM26</t>
+          <t>1063796-29-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25212,32 +25216,32 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K396" t="inlineStr"/>
@@ -25247,13 +25251,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>3418.36</v>
+        <v>4354.63</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>4429-340-CM26</t>
+          <t>2345-323-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -25278,27 +25282,27 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>69.264.400-k</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HUALPEN</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -25312,13 +25316,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>833.46</v>
+        <v>2369.62</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>539119-2507-CM26</t>
+          <t>1078078-2477-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -25338,17 +25342,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -25358,12 +25362,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K398" t="inlineStr"/>
@@ -25373,6 +25377,132 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
+        <v>3418.36</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>4429-340-CM26</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>69.264.400-k</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE HUALPEN</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="n">
+        <v>833.46</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>539119-2507-CM26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>60.505.720-9</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="n">
         <v>52017.3</v>
       </c>
     </row>
